--- a/apps_results_MAK_REINFORCE/multistability_2species_6rxns/multistability_2species_6rxns_MAK_REINFORCE.xlsx
+++ b/apps_results_MAK_REINFORCE/multistability_2species_6rxns/multistability_2species_6rxns_MAK_REINFORCE.xlsx
@@ -10,14 +10,14 @@
     <sheet r:id="rId1" sheetId="1" name="Data"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Data'!$A$1:$W$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Data'!$A$1:$W$26</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="119">
   <si>
     <t>Timestamp</t>
   </si>
@@ -196,10 +196,184 @@
     <t>https://www.comet.com/maurice-filo/multistability-2species-6rxns-mak-reinforce/4d96bd5ac0b44e62a09503b8179f04cf</t>
   </si>
   <si>
-    <t>run-8. Set the entropy weight of the parameter head to 0.</t>
+    <t>run-8. Set the entropy weight of the parameter head to 0. No convergence.</t>
   </si>
   <si>
     <t>{'entropy_weight': 0.001, 'entropy_weight_structure_head': 10.0, 'entropy_weight_continuous_head': 0.0, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+  </si>
+  <si>
+    <t>2025-12-05 14:19:10</t>
+  </si>
+  <si>
+    <t>https://www.comet.com/maurice-filo/multistability-2species-6rxns-mak-reinforce/edc8873a854548fb9ddd8b8b89f46d71</t>
+  </si>
+  <si>
+    <t>run-9. Reset the entropy weights to those in run-7. Decreased the risk to 0.9. SIL added. No convergence.</t>
+  </si>
+  <si>
+    <t>2025-12-05 15:49:48</t>
+  </si>
+  <si>
+    <t>https://www.comet.com/maurice-filo/multistability-2species-6rxns-mak-reinforce/1e3b4f2cf5e2415abf02e34352ad9f0f</t>
+  </si>
+  <si>
+    <t>run-10. Same conditions as run-5. But with SIL weight of 0.1. Convergence consistency was improved significantly. But it didn't converge to good values.</t>
+  </si>
+  <si>
+    <t>2025-12-05 20:11:21</t>
+  </si>
+  <si>
+    <t>https://www.comet.com/maurice-filo/multistability-2species-6rxns-mak-reinforce/f481465fe70c404f91601b5744e178c3</t>
+  </si>
+  <si>
+    <t>run-11. Increase the entropy weight of the structure head 10 folds. Increased the number of epochs. Similar to previous run.</t>
+  </si>
+  <si>
+    <t>2025-12-05 23:52:51</t>
+  </si>
+  <si>
+    <t>https://www.comet.com/maurice-filo/multistability-2species-6rxns-mak-reinforce/339f7bb770e242e58dceaa449932c465</t>
+  </si>
+  <si>
+    <t>Yes/No</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>run-12. Increased the weight of SIL. Converged. But got only one topology.</t>
+  </si>
+  <si>
+    <t>2025-12-06 06:55:37</t>
+  </si>
+  <si>
+    <t>https://www.comet.com/maurice-filo/multistability-2species-6rxns-mak-reinforce/d5f1d705b0564f538d3f84d4684feee1</t>
+  </si>
+  <si>
+    <t>run-13. Same conditions as previous run, but loss function looks only at endpoints of the dynamics. Similar to before.</t>
+  </si>
+  <si>
+    <t>2025-12-06 11:22:20</t>
+  </si>
+  <si>
+    <t>https://www.comet.com/maurice-filo/multistability-2species-6rxns-mak-reinforce/57968c287b904e99a24a4f71bc07877c</t>
+  </si>
+  <si>
+    <t>run-14. Increased the weight on the topk entropy compared to the rest of the batch.</t>
+  </si>
+  <si>
+    <t>{'entropy_weight': 0.001, 'entropy_weight_structure_head': 10.0, 'entropy_weight_continuous_head': 0.01, 'topk_entropy_weight': 5.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+  </si>
+  <si>
+    <t>2025-12-06 13:40:18</t>
+  </si>
+  <si>
+    <t>https://www.comet.com/maurice-filo/multistability-2species-6rxns-mak-reinforce/dc859ce96f764083944c0c4a0db05892</t>
+  </si>
+  <si>
+    <t>run-15. Increased the weight on the topk entropy compared to the rest of the batch even more.</t>
+  </si>
+  <si>
+    <t>{'entropy_weight': 0.001, 'entropy_weight_structure_head': 10.0, 'entropy_weight_continuous_head': 0.01, 'topk_entropy_weight': 10.0, 'remainder_entropy_weight': 0.01, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+  </si>
+  <si>
+    <t>2025-12-06 18:30:45</t>
+  </si>
+  <si>
+    <t>https://www.comet.com/maurice-filo/multistability-2species-6rxns-mak-reinforce/f1da4a75c296464a8b221626501eba1b</t>
+  </si>
+  <si>
+    <t>run-16. Set the risk to 0.9. Reset the entropy weights. Convergence speed was good. Still not seeing diversity, but it's not too bad.</t>
+  </si>
+  <si>
+    <t>2025-12-07 08:34:36</t>
+  </si>
+  <si>
+    <t>https://www.comet.com/maurice-filo/multistability-2species-6rxns-mak-reinforce/c9203d781daa43128846593ff80ac019</t>
+  </si>
+  <si>
+    <t>run-17.  Good convergence. Got one topology</t>
+  </si>
+  <si>
+    <t>2025-12-07 13:06:42</t>
+  </si>
+  <si>
+    <t>https://www.comet.com/maurice-filo/multistability-2species-6rxns-mak-reinforce/97096af0b57d431fa4e64f7d6bc98064</t>
+  </si>
+  <si>
+    <t>run-18. Increased the entropy weight of the structure head 5 times. Too slow of a convergence. Need more epochs.</t>
+  </si>
+  <si>
+    <t>{'entropy_weight': 0.001, 'entropy_weight_structure_head': 50.0, 'entropy_weight_continuous_head': 1.0, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+  </si>
+  <si>
+    <t>2025-12-07 14:53:31</t>
+  </si>
+  <si>
+    <t>https://www.comet.com/maurice-filo/multistability-2species-6rxns-mak-reinforce/ec0a7da213e1428c869ec00976c9f294</t>
+  </si>
+  <si>
+    <t>Yes*</t>
+  </si>
+  <si>
+    <t>run-19. Doubled number of epochs. Seems to be a succesful run.</t>
+  </si>
+  <si>
+    <t>2025-12-07 22:12:41</t>
+  </si>
+  <si>
+    <t>https://www.comet.com/maurice-filo/multistability-2species-6rxns-mak-reinforce/59e18c7c49134d70b33e55d9b6e0144f</t>
+  </si>
+  <si>
+    <t>run-20. Same conditions as previous run. Too spiky, and got one topology.</t>
+  </si>
+  <si>
+    <t>2025-12-08 07:44:18</t>
+  </si>
+  <si>
+    <t>https://www.comet.com/maurice-filo/multistability-2species-6rxns-mak-reinforce/76d87f9dde284223812d2d1707343c24</t>
+  </si>
+  <si>
+    <t>run-21. Decreased the entropy weight of the structure head a little, and that of the parameter head as well. Run was very succesfull with high generative power.</t>
+  </si>
+  <si>
+    <t>{'entropy_weight': 0.001, 'entropy_weight_structure_head': 30.0, 'entropy_weight_continuous_head': 0.3, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+  </si>
+  <si>
+    <t>2025-12-19 14:39:13</t>
+  </si>
+  <si>
+    <t>https://www.comet.com/maurice-filo/multistability-2species-6rxns-mak-reinforce/8066249b9a014ddc8c98efaeb42a1cef</t>
+  </si>
+  <si>
+    <t>run-22. Set the entropy weights to 10 and 0.1. Successful run.</t>
+  </si>
+  <si>
+    <t>2025-12-19 19:19:36</t>
+  </si>
+  <si>
+    <t>https://www.comet.com/maurice-filo/multistability-2species-6rxns-mak-reinforce/276fa11694174e3cbdd726a485b23bae</t>
+  </si>
+  <si>
+    <t>run-23. Same conditions as before. Run results are okay</t>
+  </si>
+  <si>
+    <t>2025-12-22 15:08:28</t>
+  </si>
+  <si>
+    <t>https://www.comet.com/maurice-filo/multistability-2species-6rxns-mak-reinforce/0993e0c48ccd4d07b1fb67ae60467c13</t>
+  </si>
+  <si>
+    <t>run-24. Same conditions as run-21. Succesful.</t>
+  </si>
+  <si>
+    <t>2025-12-23 20:46:46</t>
+  </si>
+  <si>
+    <t>https://www.comet.com/maurice-filo/multistability-2species-6rxns-mak-reinforce/f08e0486aa074a20944833eba670feca</t>
+  </si>
+  <si>
+    <t>run-25. Same conditions as before. Excellent run.</t>
   </si>
 </sst>
 </file>
@@ -574,7 +748,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:W9"/>
+  <dimension ref="A1:W26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" style="4" width="20.005" customWidth="1" bestFit="1"/>
@@ -582,8 +756,8 @@
     <col min="3" max="3" style="4" width="11.005" customWidth="1" bestFit="1"/>
     <col min="4" max="4" style="4" width="17.005" customWidth="1" bestFit="1"/>
     <col min="5" max="5" style="4" width="6.005" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="4" width="94.005" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="4" width="256.005" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="4" width="161.005" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="4" width="258.005" customWidth="1" bestFit="1"/>
     <col min="8" max="8" style="4" width="14.005" customWidth="1" bestFit="1"/>
     <col min="9" max="9" style="5" width="9.005" customWidth="1" bestFit="1"/>
     <col min="10" max="10" style="4" width="16.005" customWidth="1" bestFit="1"/>
@@ -602,7 +776,7 @@
     <col min="23" max="23" style="4" width="133.005" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -673,7 +847,7 @@
         <v>22</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
       <c r="A2" s="1" t="s">
         <v>23</v>
       </c>
@@ -744,7 +918,7 @@
         <v>32</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
       <c r="A3" s="1" t="s">
         <v>33</v>
       </c>
@@ -815,7 +989,7 @@
         <v>32</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
       <c r="A4" s="1" t="s">
         <v>37</v>
       </c>
@@ -886,7 +1060,7 @@
         <v>32</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
       <c r="A5" s="1" t="s">
         <v>41</v>
       </c>
@@ -957,7 +1131,7 @@
         <v>32</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
       <c r="A6" s="1" t="s">
         <v>45</v>
       </c>
@@ -1028,7 +1202,7 @@
         <v>32</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
       <c r="A7" s="1" t="s">
         <v>49</v>
       </c>
@@ -1099,7 +1273,7 @@
         <v>32</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
       <c r="A8" s="1" t="s">
         <v>53</v>
       </c>
@@ -1170,16 +1344,22 @@
         <v>32</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
       <c r="A9" s="1" t="s">
         <v>57</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
+      <c r="C9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>25</v>
+      </c>
       <c r="F9" s="1" t="s">
         <v>59</v>
       </c>
@@ -1189,49 +1369,1256 @@
       <c r="H9" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="I9" s="3">
+      <c r="I9" s="2">
         <v>400</v>
       </c>
       <c r="J9" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="K9" s="3">
+      <c r="K9" s="2">
         <v>5</v>
       </c>
-      <c r="L9" s="3">
+      <c r="L9" s="2">
         <v>1024</v>
       </c>
-      <c r="M9" s="3">
+      <c r="M9" s="2">
         <v>10240</v>
       </c>
-      <c r="N9" s="3">
+      <c r="N9" s="2">
         <v>128</v>
       </c>
       <c r="O9" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="P9" s="3">
-        <v>10</v>
-      </c>
-      <c r="Q9" s="3">
-        <v>30</v>
-      </c>
-      <c r="R9" s="3">
+      <c r="P9" s="2">
+        <v>10</v>
+      </c>
+      <c r="Q9" s="2">
+        <v>30</v>
+      </c>
+      <c r="R9" s="2">
         <v>100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="S9" s="2">
         <v>1000</v>
       </c>
-      <c r="T9" s="3">
-        <v>32</v>
-      </c>
-      <c r="U9" s="3">
+      <c r="T9" s="2">
+        <v>32</v>
+      </c>
+      <c r="U9" s="2">
         <v>1</v>
       </c>
       <c r="V9" s="1" t="s">
         <v>31</v>
       </c>
       <c r="W9" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
+      <c r="A10" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I10" s="2">
+        <v>400</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K10" s="2">
+        <v>5</v>
+      </c>
+      <c r="L10" s="2">
+        <v>1024</v>
+      </c>
+      <c r="M10" s="2">
+        <v>10240</v>
+      </c>
+      <c r="N10" s="2">
+        <v>128</v>
+      </c>
+      <c r="O10" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P10" s="2">
+        <v>10</v>
+      </c>
+      <c r="Q10" s="2">
+        <v>30</v>
+      </c>
+      <c r="R10" s="2">
+        <v>100</v>
+      </c>
+      <c r="S10" s="2">
+        <v>1000</v>
+      </c>
+      <c r="T10" s="2">
+        <v>32</v>
+      </c>
+      <c r="U10" s="2">
+        <v>1</v>
+      </c>
+      <c r="V10" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="W10" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
+      <c r="A11" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I11" s="2">
+        <v>400</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K11" s="2">
+        <v>5</v>
+      </c>
+      <c r="L11" s="2">
+        <v>1024</v>
+      </c>
+      <c r="M11" s="2">
+        <v>10240</v>
+      </c>
+      <c r="N11" s="2">
+        <v>128</v>
+      </c>
+      <c r="O11" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="P11" s="2">
+        <v>10</v>
+      </c>
+      <c r="Q11" s="2">
+        <v>30</v>
+      </c>
+      <c r="R11" s="2">
+        <v>100</v>
+      </c>
+      <c r="S11" s="2">
+        <v>1000</v>
+      </c>
+      <c r="T11" s="2">
+        <v>32</v>
+      </c>
+      <c r="U11" s="2">
+        <v>1</v>
+      </c>
+      <c r="V11" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="W11" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
+      <c r="A12" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I12" s="2">
+        <v>800</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K12" s="2">
+        <v>5</v>
+      </c>
+      <c r="L12" s="2">
+        <v>1024</v>
+      </c>
+      <c r="M12" s="2">
+        <v>10240</v>
+      </c>
+      <c r="N12" s="2">
+        <v>128</v>
+      </c>
+      <c r="O12" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="P12" s="2">
+        <v>10</v>
+      </c>
+      <c r="Q12" s="2">
+        <v>30</v>
+      </c>
+      <c r="R12" s="2">
+        <v>100</v>
+      </c>
+      <c r="S12" s="2">
+        <v>1000</v>
+      </c>
+      <c r="T12" s="2">
+        <v>32</v>
+      </c>
+      <c r="U12" s="2">
+        <v>1</v>
+      </c>
+      <c r="V12" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="W12" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
+      <c r="A13" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I13" s="2">
+        <v>800</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K13" s="2">
+        <v>5</v>
+      </c>
+      <c r="L13" s="2">
+        <v>1024</v>
+      </c>
+      <c r="M13" s="2">
+        <v>10240</v>
+      </c>
+      <c r="N13" s="2">
+        <v>128</v>
+      </c>
+      <c r="O13" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="P13" s="2">
+        <v>10</v>
+      </c>
+      <c r="Q13" s="2">
+        <v>30</v>
+      </c>
+      <c r="R13" s="2">
+        <v>100</v>
+      </c>
+      <c r="S13" s="2">
+        <v>1000</v>
+      </c>
+      <c r="T13" s="2">
+        <v>32</v>
+      </c>
+      <c r="U13" s="2">
+        <v>1</v>
+      </c>
+      <c r="V13" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="W13" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
+      <c r="A14" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I14" s="2">
+        <v>800</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K14" s="2">
+        <v>5</v>
+      </c>
+      <c r="L14" s="2">
+        <v>1024</v>
+      </c>
+      <c r="M14" s="2">
+        <v>10240</v>
+      </c>
+      <c r="N14" s="2">
+        <v>128</v>
+      </c>
+      <c r="O14" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="P14" s="2">
+        <v>10</v>
+      </c>
+      <c r="Q14" s="2">
+        <v>30</v>
+      </c>
+      <c r="R14" s="2">
+        <v>100</v>
+      </c>
+      <c r="S14" s="2">
+        <v>1000</v>
+      </c>
+      <c r="T14" s="2">
+        <v>32</v>
+      </c>
+      <c r="U14" s="2">
+        <v>1</v>
+      </c>
+      <c r="V14" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="W14" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5">
+      <c r="A15" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I15" s="2">
+        <v>800</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K15" s="2">
+        <v>5</v>
+      </c>
+      <c r="L15" s="2">
+        <v>1024</v>
+      </c>
+      <c r="M15" s="2">
+        <v>10240</v>
+      </c>
+      <c r="N15" s="2">
+        <v>128</v>
+      </c>
+      <c r="O15" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="P15" s="2">
+        <v>10</v>
+      </c>
+      <c r="Q15" s="2">
+        <v>30</v>
+      </c>
+      <c r="R15" s="2">
+        <v>100</v>
+      </c>
+      <c r="S15" s="2">
+        <v>1000</v>
+      </c>
+      <c r="T15" s="2">
+        <v>32</v>
+      </c>
+      <c r="U15" s="2">
+        <v>1</v>
+      </c>
+      <c r="V15" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="W15" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="19.5">
+      <c r="A16" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I16" s="2">
+        <v>800</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K16" s="2">
+        <v>5</v>
+      </c>
+      <c r="L16" s="2">
+        <v>1024</v>
+      </c>
+      <c r="M16" s="2">
+        <v>10240</v>
+      </c>
+      <c r="N16" s="2">
+        <v>128</v>
+      </c>
+      <c r="O16" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="P16" s="2">
+        <v>10</v>
+      </c>
+      <c r="Q16" s="2">
+        <v>30</v>
+      </c>
+      <c r="R16" s="2">
+        <v>100</v>
+      </c>
+      <c r="S16" s="2">
+        <v>1000</v>
+      </c>
+      <c r="T16" s="2">
+        <v>32</v>
+      </c>
+      <c r="U16" s="2">
+        <v>1</v>
+      </c>
+      <c r="V16" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="W16" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="19.5">
+      <c r="A17" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I17" s="2">
+        <v>400</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K17" s="2">
+        <v>5</v>
+      </c>
+      <c r="L17" s="2">
+        <v>1024</v>
+      </c>
+      <c r="M17" s="2">
+        <v>10240</v>
+      </c>
+      <c r="N17" s="2">
+        <v>128</v>
+      </c>
+      <c r="O17" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P17" s="2">
+        <v>10</v>
+      </c>
+      <c r="Q17" s="2">
+        <v>30</v>
+      </c>
+      <c r="R17" s="2">
+        <v>100</v>
+      </c>
+      <c r="S17" s="2">
+        <v>1000</v>
+      </c>
+      <c r="T17" s="2">
+        <v>32</v>
+      </c>
+      <c r="U17" s="2">
+        <v>1</v>
+      </c>
+      <c r="V17" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="W17" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5">
+      <c r="A18" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I18" s="2">
+        <v>400</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K18" s="2">
+        <v>5</v>
+      </c>
+      <c r="L18" s="2">
+        <v>1024</v>
+      </c>
+      <c r="M18" s="2">
+        <v>10240</v>
+      </c>
+      <c r="N18" s="2">
+        <v>128</v>
+      </c>
+      <c r="O18" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P18" s="2">
+        <v>10</v>
+      </c>
+      <c r="Q18" s="2">
+        <v>10</v>
+      </c>
+      <c r="R18" s="2">
+        <v>100</v>
+      </c>
+      <c r="S18" s="2">
+        <v>1000</v>
+      </c>
+      <c r="T18" s="2">
+        <v>32</v>
+      </c>
+      <c r="U18" s="2">
+        <v>1</v>
+      </c>
+      <c r="V18" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="W18" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="19.5">
+      <c r="A19" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I19" s="2">
+        <v>400</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K19" s="2">
+        <v>5</v>
+      </c>
+      <c r="L19" s="2">
+        <v>1024</v>
+      </c>
+      <c r="M19" s="2">
+        <v>10240</v>
+      </c>
+      <c r="N19" s="2">
+        <v>128</v>
+      </c>
+      <c r="O19" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P19" s="2">
+        <v>10</v>
+      </c>
+      <c r="Q19" s="2">
+        <v>10</v>
+      </c>
+      <c r="R19" s="2">
+        <v>100</v>
+      </c>
+      <c r="S19" s="2">
+        <v>1000</v>
+      </c>
+      <c r="T19" s="2">
+        <v>32</v>
+      </c>
+      <c r="U19" s="2">
+        <v>1</v>
+      </c>
+      <c r="V19" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="W19" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="19.5">
+      <c r="A20" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I20" s="2">
+        <v>800</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K20" s="2">
+        <v>5</v>
+      </c>
+      <c r="L20" s="2">
+        <v>1024</v>
+      </c>
+      <c r="M20" s="2">
+        <v>10240</v>
+      </c>
+      <c r="N20" s="2">
+        <v>128</v>
+      </c>
+      <c r="O20" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P20" s="2">
+        <v>10</v>
+      </c>
+      <c r="Q20" s="2">
+        <v>10</v>
+      </c>
+      <c r="R20" s="2">
+        <v>100</v>
+      </c>
+      <c r="S20" s="2">
+        <v>1000</v>
+      </c>
+      <c r="T20" s="2">
+        <v>32</v>
+      </c>
+      <c r="U20" s="2">
+        <v>1</v>
+      </c>
+      <c r="V20" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="W20" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="19.5">
+      <c r="A21" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I21" s="2">
+        <v>800</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K21" s="2">
+        <v>5</v>
+      </c>
+      <c r="L21" s="2">
+        <v>1024</v>
+      </c>
+      <c r="M21" s="2">
+        <v>10240</v>
+      </c>
+      <c r="N21" s="2">
+        <v>128</v>
+      </c>
+      <c r="O21" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P21" s="2">
+        <v>10</v>
+      </c>
+      <c r="Q21" s="2">
+        <v>10</v>
+      </c>
+      <c r="R21" s="2">
+        <v>100</v>
+      </c>
+      <c r="S21" s="2">
+        <v>1000</v>
+      </c>
+      <c r="T21" s="2">
+        <v>32</v>
+      </c>
+      <c r="U21" s="2">
+        <v>1</v>
+      </c>
+      <c r="V21" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="W21" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="19.5">
+      <c r="A22" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I22" s="2">
+        <v>800</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K22" s="2">
+        <v>5</v>
+      </c>
+      <c r="L22" s="2">
+        <v>1024</v>
+      </c>
+      <c r="M22" s="2">
+        <v>10240</v>
+      </c>
+      <c r="N22" s="2">
+        <v>128</v>
+      </c>
+      <c r="O22" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P22" s="2">
+        <v>10</v>
+      </c>
+      <c r="Q22" s="2">
+        <v>10</v>
+      </c>
+      <c r="R22" s="2">
+        <v>100</v>
+      </c>
+      <c r="S22" s="2">
+        <v>1000</v>
+      </c>
+      <c r="T22" s="2">
+        <v>32</v>
+      </c>
+      <c r="U22" s="2">
+        <v>1</v>
+      </c>
+      <c r="V22" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="W22" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="19.5">
+      <c r="A23" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I23" s="2">
+        <v>800</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K23" s="2">
+        <v>5</v>
+      </c>
+      <c r="L23" s="2">
+        <v>1024</v>
+      </c>
+      <c r="M23" s="2">
+        <v>10240</v>
+      </c>
+      <c r="N23" s="2">
+        <v>128</v>
+      </c>
+      <c r="O23" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P23" s="2">
+        <v>10</v>
+      </c>
+      <c r="Q23" s="2">
+        <v>10</v>
+      </c>
+      <c r="R23" s="2">
+        <v>100</v>
+      </c>
+      <c r="S23" s="2">
+        <v>1000</v>
+      </c>
+      <c r="T23" s="2">
+        <v>32</v>
+      </c>
+      <c r="U23" s="2">
+        <v>1</v>
+      </c>
+      <c r="V23" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="W23" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="19.5">
+      <c r="A24" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I24" s="2">
+        <v>800</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K24" s="2">
+        <v>5</v>
+      </c>
+      <c r="L24" s="2">
+        <v>1024</v>
+      </c>
+      <c r="M24" s="2">
+        <v>10240</v>
+      </c>
+      <c r="N24" s="2">
+        <v>128</v>
+      </c>
+      <c r="O24" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P24" s="2">
+        <v>10</v>
+      </c>
+      <c r="Q24" s="2">
+        <v>10</v>
+      </c>
+      <c r="R24" s="2">
+        <v>100</v>
+      </c>
+      <c r="S24" s="2">
+        <v>1000</v>
+      </c>
+      <c r="T24" s="2">
+        <v>32</v>
+      </c>
+      <c r="U24" s="2">
+        <v>1</v>
+      </c>
+      <c r="V24" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="W24" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="19.5">
+      <c r="A25" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I25" s="2">
+        <v>800</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K25" s="2">
+        <v>5</v>
+      </c>
+      <c r="L25" s="2">
+        <v>1024</v>
+      </c>
+      <c r="M25" s="2">
+        <v>10240</v>
+      </c>
+      <c r="N25" s="2">
+        <v>128</v>
+      </c>
+      <c r="O25" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P25" s="2">
+        <v>10</v>
+      </c>
+      <c r="Q25" s="2">
+        <v>30</v>
+      </c>
+      <c r="R25" s="2">
+        <v>100</v>
+      </c>
+      <c r="S25" s="2">
+        <v>1000</v>
+      </c>
+      <c r="T25" s="2">
+        <v>32</v>
+      </c>
+      <c r="U25" s="2">
+        <v>1</v>
+      </c>
+      <c r="V25" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="W25" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="17.25">
+      <c r="A26" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I26" s="3">
+        <v>800</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K26" s="3">
+        <v>5</v>
+      </c>
+      <c r="L26" s="3">
+        <v>1024</v>
+      </c>
+      <c r="M26" s="3">
+        <v>10240</v>
+      </c>
+      <c r="N26" s="3">
+        <v>128</v>
+      </c>
+      <c r="O26" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P26" s="3">
+        <v>10</v>
+      </c>
+      <c r="Q26" s="3">
+        <v>30</v>
+      </c>
+      <c r="R26" s="3">
+        <v>100</v>
+      </c>
+      <c r="S26" s="3">
+        <v>1000</v>
+      </c>
+      <c r="T26" s="3">
+        <v>32</v>
+      </c>
+      <c r="U26" s="3">
+        <v>1</v>
+      </c>
+      <c r="V26" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="W26" s="1" t="s">
         <v>32</v>
       </c>
     </row>
